--- a/Questions - Round 7.xlsx
+++ b/Questions - Round 7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_A92674D4C910BAB53AFAAD35F6979E35FDF17E66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D377285A-BD11-4FFD-8187-9D9510DD7B3F}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_A92674D4C910BAB53AFAAD35F6979E35FDF17E66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA78855C-B85B-4557-951B-32D337804E97}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,23 @@
     <sheet name="IT" sheetId="6" r:id="rId6"/>
     <sheet name="PL" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,16 +83,16 @@
     <t>Easy · Single choice</t>
   </si>
   <si>
-    <t>It asks companies to ignore long-term impacts.</t>
-  </si>
-  <si>
-    <t>It is only a marketing slogan with no practical meaning.</t>
+    <t>It mainly seeks to make individual production steps more efficient, regardless of consumption patterns.</t>
+  </si>
+  <si>
+    <t>It primarily promotes voluntary communication about sustainable products without addressing resource use.</t>
   </si>
   <si>
     <t>It focuses on responsible resource use and circularity.</t>
   </si>
   <si>
-    <t>It only applies to national governments.</t>
+    <t>It mainly aims to expand recycling capacity, while other stages of the product life cycle are secondary.</t>
   </si>
   <si>
     <t>SDG 12 is about responsible resource use and circularity and turning that goal into practical action. SDG 12 becomes useful when people translate the broad goal into practical decisions.</t>
@@ -88,13 +104,13 @@
     <t>Medium · Single choice</t>
   </si>
   <si>
-    <t>Because sustainability only belongs in annual reports.</t>
-  </si>
-  <si>
-    <t>Because the SDGs replace all legal requirements.</t>
-  </si>
-  <si>
-    <t>Because chemicals have no link with sustainability.</t>
+    <t>Because documented environmental targets mainly create transparency but have little influence on operations.</t>
+  </si>
+  <si>
+    <t>Because the SDGs complement legal requirements as a voluntary framework and largely replace legal reviews.</t>
+  </si>
+  <si>
+    <t>Because sustainability in chemicals mainly concerns production energy use, not distribution.</t>
   </si>
   <si>
     <t>Because packaging, recycling and supplier responsibility can influence sustainability performance.</t>
@@ -106,7 +122,7 @@
     <t>Which statement is a common misunderstanding about SDG 12?</t>
   </si>
   <si>
-    <t>Recycling alone solves all consumption problems.</t>
+    <t>Consistent recycling alone is sufficient to achieve the main objectives of SDG 12.</t>
   </si>
   <si>
     <t>SDG 12 can be linked to daily decisions.</t>
@@ -124,16 +140,16 @@
     <t>Which behaviour best turns SDG 12 from theory into action?</t>
   </si>
   <si>
-    <t>Waiting until someone else fixes everything.</t>
-  </si>
-  <si>
-    <t>Choosing a concrete improvement and following through.</t>
-  </si>
-  <si>
-    <t>Talking about sustainability but changing nothing.</t>
-  </si>
-  <si>
-    <t>Doing the opposite when nobody is checking.</t>
+    <t>Wait for uniform industry standards before starting individual improvements.</t>
+  </si>
+  <si>
+    <t>Choose a concrete improvement and follow it through consistently.</t>
+  </si>
+  <si>
+    <t>Record targets in guidelines first and postpone implementation to a later reporting period.</t>
+  </si>
+  <si>
+    <t>Pursue improvements only where short-term cost savings can be demonstrated with certainty.</t>
   </si>
   <si>
     <t>Concrete action creates learning and measurable improvement. Sustainability awareness should lead to practical behaviour change.</t>
@@ -142,16 +158,16 @@
     <t>What makes SDG 12 a useful learning topic for employees?</t>
   </si>
   <si>
-    <t>It is unrelated to company culture.</t>
-  </si>
-  <si>
-    <t>It removes the need for expert knowledge.</t>
+    <t>It provides uniform rules of conduct that largely replace individual judgement.</t>
+  </si>
+  <si>
+    <t>It enables sustainability decisions without considering specialist knowledge of risks and regulations.</t>
   </si>
   <si>
     <t>It links global challenges to choices people recognise at work and at home.</t>
   </si>
   <si>
-    <t>It gives one perfect answer for every situation.</t>
+    <t>It provides a fixed catalogue of measures that can be applied equally across all business areas.</t>
   </si>
   <si>
     <t>The strongest learning happens when people see the link between global goals and familiar choices. The SDGs are most engaging when they feel relevant, concrete and connected to people’s roles.</t>
@@ -160,13 +176,13 @@
     <t>How much reusable packaging did STOCKMEIER Chemie bring into circulation?</t>
   </si>
   <si>
-    <t>Zero tons</t>
-  </si>
-  <si>
-    <t>Only one pallet</t>
-  </si>
-  <si>
-    <t>6.2 kilograms</t>
+    <t>625.54 tons</t>
+  </si>
+  <si>
+    <t>6,255.4 kilograms</t>
+  </si>
+  <si>
+    <t>62,554 tons</t>
   </si>
   <si>
     <t>6,255.4 tons</t>
@@ -184,13 +200,13 @@
     <t>Cardboard, pallets and films</t>
   </si>
   <si>
-    <t>All hazardous waste liquids</t>
-  </si>
-  <si>
-    <t>Only office coffee cups</t>
-  </si>
-  <si>
-    <t>All raw materials worldwide</t>
+    <t>Glass, metal drums and IBCs</t>
+  </si>
+  <si>
+    <t>Cardboard, office paper and wood</t>
+  </si>
+  <si>
+    <t>Plastic films, canisters and drums</t>
   </si>
   <si>
     <t>The report states cardboard, pallets and films are 100% recycled. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
@@ -199,16 +215,16 @@
     <t>What does the drum clip example show?</t>
   </si>
   <si>
-    <t>Waste should always be ignored</t>
-  </si>
-  <si>
-    <t>Circular thinking can reduce waste and new purchases</t>
-  </si>
-  <si>
-    <t>Small materials never matter</t>
-  </si>
-  <si>
-    <t>Reuse is impossible across sites</t>
+    <t>Reuse is most worthwhile when return transport is organised centrally.</t>
+  </si>
+  <si>
+    <t>Circular thinking can reduce waste and new purchases.</t>
+  </si>
+  <si>
+    <t>Small materials should only be considered once they represent a large share of waste by weight.</t>
+  </si>
+  <si>
+    <t>Reuse across sites requires identical procurement processes.</t>
   </si>
   <si>
     <t>The report describes 650 drum clips being returned for reuse, reducing material consumption and cost. STOCKMEIER examples make the SDG concrete and show how Group initiatives connect to global goals.</t>
@@ -217,16 +233,16 @@
     <t>At home, which action best supports SDG 12?</t>
   </si>
   <si>
-    <t>Buying more than needed</t>
-  </si>
-  <si>
-    <t>Throwing away usable products</t>
-  </si>
-  <si>
-    <t>Repairing or reusing items before replacing them</t>
-  </si>
-  <si>
-    <t>Ignoring waste sorting</t>
+    <t>Choose products with recyclable packaging even if they need to be replaced sooner.</t>
+  </si>
+  <si>
+    <t>Replace older but functional appliances whenever a more efficient version becomes available.</t>
+  </si>
+  <si>
+    <t>Repair or reuse items before replacing them.</t>
+  </si>
+  <si>
+    <t>Buy bulk packs to reduce packaging per unit even if some of the contents remain unused.</t>
   </si>
   <si>
     <t>Reuse and repair reduce resource demand. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
@@ -235,16 +251,16 @@
     <t>Which shopping habit supports responsible consumption?</t>
   </si>
   <si>
-    <t>Ignoring product lifespan</t>
-  </si>
-  <si>
-    <t>Buying duplicates without need</t>
-  </si>
-  <si>
-    <t>Choosing excessive packaging every time</t>
-  </si>
-  <si>
-    <t>Planning purchases to avoid waste</t>
+    <t>Always choose the cheapest product even if it has a shorter service life.</t>
+  </si>
+  <si>
+    <t>Stock up on discounted products without checking existing supplies.</t>
+  </si>
+  <si>
+    <t>Use recyclable packaging as the only criterion regardless of the quantity needed.</t>
+  </si>
+  <si>
+    <t>Plan purchases to avoid waste.</t>
   </si>
   <si>
     <t>Planning reduces unnecessary consumption and waste. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
@@ -256,16 +272,16 @@
     <t>Makkelijk · Eén antwoord</t>
   </si>
   <si>
-    <t>Het vraagt bedrijven om langetermijneffecten te negeren.</t>
-  </si>
-  <si>
-    <t>Het is alleen een marketingslogan zonder praktische betekenis.</t>
+    <t>Het gaat er vooral om afzonderlijke productiestappen efficiënter te maken, ongeacht het consumptiegedrag.</t>
+  </si>
+  <si>
+    <t>Het bevordert vooral vrijwillige communicatie over duurzame producten, zonder het gebruik van hulpbronnen mee te nemen.</t>
   </si>
   <si>
     <t>Het richt zich op verantwoord gebruik van hulpbronnen en circulariteit.</t>
   </si>
   <si>
-    <t>Het is alleen van toepassing op nationale overheden.</t>
+    <t>Het is hoofdzakelijk gericht op uitbreiding van de recyclingcapaciteit; andere fasen van de productlevenscyclus zijn ondergeschikt.</t>
   </si>
   <si>
     <t>SDG 12 gaat over verantwoord gebruik van hulpbronnen en circulariteit, en over het omzetten van dat doel in concrete actie. SDG 12 wordt nuttig wanneer mensen het brede doel vertalen naar praktische beslissingen.</t>
@@ -277,13 +293,13 @@
     <t>Gemiddeld · Eén antwoord</t>
   </si>
   <si>
-    <t>Omdat duurzaamheid alleen thuishoort in jaarverslagen.</t>
-  </si>
-  <si>
-    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
-  </si>
-  <si>
-    <t>Omdat chemicaliën geen verband houden met duurzaamheid.</t>
+    <t>Omdat vastgelegde milieudoelen vooral transparantie creëren, maar weinig invloed hebben op de bedrijfsvoering.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's wettelijke eisen aanvullen als vrijwillig kader en juridische controles grotendeels vervangen.</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid in de chemie vooral het energiegebruik in de productie betreft, niet de distributie.</t>
   </si>
   <si>
     <t>Omdat verpakkingen, recycling en verantwoordelijkheid van leveranciers de duurzaamheidsprestaties kunnen beïnvloeden.</t>
@@ -295,7 +311,7 @@
     <t>Welke uitspraak is een veelvoorkomend misverstand over SDG 12?</t>
   </si>
   <si>
-    <t>Alleen recycling lost alle consumptieproblemen op.</t>
+    <t>Consequente recycling alleen is voldoende om de belangrijkste doelen van SDG 12 te bereiken.</t>
   </si>
   <si>
     <t>SDG 12 kan worden gekoppeld aan dagelijkse beslissingen.</t>
@@ -313,16 +329,16 @@
     <t>Welk gedrag zet SDG 12 het best om van theorie naar actie?</t>
   </si>
   <si>
-    <t>Wachten tot iemand anders alles oplost.</t>
-  </si>
-  <si>
-    <t>Een concrete verbetering kiezen en die ook uitvoeren.</t>
-  </si>
-  <si>
-    <t>Over duurzaamheid praten, maar niets veranderen.</t>
-  </si>
-  <si>
-    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+    <t>Wachten op uniforme branchenormen voordat afzonderlijke verbeteringen worden gestart.</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die consequent uitvoeren.</t>
+  </si>
+  <si>
+    <t>Doelen eerst in richtlijnen vastleggen en de uitvoering uitstellen tot een latere verslagperiode.</t>
+  </si>
+  <si>
+    <t>Alleen verbeteringen nastreven waarvan de kostenbesparing op korte termijn zeker aantoonbaar is.</t>
   </si>
   <si>
     <t>Concrete actie leidt tot leren en meetbare verbetering. Bewustzijn rond duurzaamheid moet leiden tot praktische gedragsverandering.</t>
@@ -331,16 +347,16 @@
     <t>Wat maakt SDG 12 een nuttig leerthema voor medewerkers?</t>
   </si>
   <si>
-    <t>Het houdt geen verband met de bedrijfscultuur.</t>
-  </si>
-  <si>
-    <t>Het maakt vakkennis overbodig.</t>
+    <t>Het biedt uniforme gedragsregels die individuele afwegingen grotendeels vervangen.</t>
+  </si>
+  <si>
+    <t>Het maakt duurzaamheidsbeslissingen mogelijk zonder vakkennis over risico's en voorschriften mee te nemen.</t>
   </si>
   <si>
     <t>Het verbindt wereldwijde uitdagingen met keuzes die mensen op het werk en thuis herkennen.</t>
   </si>
   <si>
-    <t>Het geeft voor elke situatie één perfect antwoord.</t>
+    <t>Het biedt een vaste lijst maatregelen die in alle bedrijfsonderdelen hetzelfde kan worden toegepast.</t>
   </si>
   <si>
     <t>Mensen leren het meest wanneer ze het verband zien tussen wereldwijde doelen en vertrouwde keuzes. De SDG's zijn het boeiendst wanneer ze relevant, concreet en verbonden met de rollen van mensen aanvoelen.</t>
@@ -349,13 +365,13 @@
     <t>Hoeveel herbruikbare verpakkingen bracht STOCKMEIER Chemie in omloop?</t>
   </si>
   <si>
-    <t>Nul ton</t>
-  </si>
-  <si>
-    <t>Slechts één pallet</t>
-  </si>
-  <si>
-    <t>6,2 kilogram</t>
+    <t>625,54 ton</t>
+  </si>
+  <si>
+    <t>6.255,4 kilogram</t>
+  </si>
+  <si>
+    <t>62.554 ton</t>
   </si>
   <si>
     <t>6.255,4 ton</t>
@@ -373,13 +389,13 @@
     <t>Karton, pallets en folies</t>
   </si>
   <si>
-    <t>Alle vloeibare gevaarlijke afvalstoffen</t>
-  </si>
-  <si>
-    <t>Alleen koffiebekers op kantoor</t>
-  </si>
-  <si>
-    <t>Alle grondstoffen wereldwijd</t>
+    <t>Glas, metalen vaten en IBC's</t>
+  </si>
+  <si>
+    <t>Karton, kantoorpapier en hout</t>
+  </si>
+  <si>
+    <t>Kunststoffolies, jerrycans en vaten</t>
   </si>
   <si>
     <t>In het verslag staat dat karton, pallets en folies voor 100% worden gerecycled. De voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe groepsinitiatieven aansluiten bij wereldwijde doelen.</t>
@@ -388,16 +404,16 @@
     <t>Wat toont het voorbeeld met de vatclips aan?</t>
   </si>
   <si>
-    <t>Afval moet altijd worden genegeerd.</t>
+    <t>Hergebruik is vooral zinvol wanneer het retourtransport centraal wordt georganiseerd.</t>
   </si>
   <si>
     <t>Circulair denken kan afval en nieuwe aankopen verminderen.</t>
   </si>
   <si>
-    <t>Kleine materialen doen er nooit toe.</t>
-  </si>
-  <si>
-    <t>Hergebruik tussen locaties is onmogelijk.</t>
+    <t>Kleine materialen moeten pas worden meegenomen als zij een groot gewichtsaandeel van het afval vormen.</t>
+  </si>
+  <si>
+    <t>Hergebruik tussen locaties vereist identieke inkoopprocessen.</t>
   </si>
   <si>
     <t>Het verslag beschrijft dat 650 vatclips werden teruggestuurd voor hergebruik, waardoor materiaalverbruik en kosten afnamen. De voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe groepsinitiatieven aansluiten bij wereldwijde doelen.</t>
@@ -406,16 +422,16 @@
     <t>Welke actie thuis ondersteunt SDG 12 het best?</t>
   </si>
   <si>
-    <t>Meer kopen dan nodig</t>
-  </si>
-  <si>
-    <t>Bruikbare producten weggooien</t>
-  </si>
-  <si>
-    <t>Artikelen repareren of hergebruiken voordat je ze vervangt</t>
-  </si>
-  <si>
-    <t>Afvalsortering negeren</t>
+    <t>Producten met recyclebare verpakking kiezen, ook als ze daardoor eerder moeten worden vervangen.</t>
+  </si>
+  <si>
+    <t>Oudere, nog werkende apparaten vervangen zodra een efficiëntere versie beschikbaar is.</t>
+  </si>
+  <si>
+    <t>Artikelen repareren of hergebruiken voordat je ze vervangt.</t>
+  </si>
+  <si>
+    <t>Grootverpakkingen kopen om verpakking per eenheid te besparen, ook als een deel ongebruikt blijft.</t>
   </si>
   <si>
     <t>Hergebruik en reparatie verminderen de vraag naar hulpbronnen. Persoonlijke gewoonten zijn belangrijk, omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
@@ -424,16 +440,16 @@
     <t>Welke winkelgewoonte ondersteunt verantwoorde consumptie?</t>
   </si>
   <si>
-    <t>De levensduur van producten negeren</t>
-  </si>
-  <si>
-    <t>Zonder noodzaak dubbele producten kopen</t>
-  </si>
-  <si>
-    <t>Elke keer kiezen voor buitensporig veel verpakking</t>
-  </si>
-  <si>
-    <t>Aankopen plannen om verspilling te voorkomen</t>
+    <t>Altijd het goedkoopste product kiezen, ook als het minder lang meegaat.</t>
+  </si>
+  <si>
+    <t>Afgeprijsde producten inslaan zonder de bestaande voorraad te controleren.</t>
+  </si>
+  <si>
+    <t>Recyclebare verpakking als enig criterium gebruiken, ongeacht de benodigde hoeveelheid.</t>
+  </si>
+  <si>
+    <t>Aankopen plannen om verspilling te voorkomen.</t>
   </si>
   <si>
     <t>Planning vermindert onnodige consumptie en afval. Persoonlijke gewoonten zijn belangrijk, omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
@@ -445,16 +461,16 @@
     <t>Facile · Choix unique</t>
   </si>
   <si>
-    <t>Il demande aux entreprises d'ignorer les impacts à long terme.</t>
-  </si>
-  <si>
-    <t>Ce n'est qu'un slogan marketing sans signification pratique.</t>
+    <t>Il vise surtout à rendre certaines étapes de production plus efficaces, indépendamment des habitudes de consommation.</t>
+  </si>
+  <si>
+    <t>Il encourage principalement la communication volontaire sur les produits durables, sans traiter l'utilisation des ressources.</t>
   </si>
   <si>
     <t>Il met l'accent sur l'utilisation responsable des ressources et la circularité.</t>
   </si>
   <si>
-    <t>Il ne s'applique qu'aux gouvernements nationaux.</t>
+    <t>Il vise principalement à développer les capacités de recyclage, les autres étapes du cycle de vie étant secondaires.</t>
   </si>
   <si>
     <t>L'ODD 12 porte sur l'utilisation responsable des ressources et la circularité, ainsi que sur la transformation de cet objectif en actions concrètes. L'ODD 12 devient utile lorsque les personnes traduisent cet objectif général en décisions pratiques.</t>
@@ -466,13 +482,13 @@
     <t>Moyen · Choix unique</t>
   </si>
   <si>
-    <t>Parce que la durabilité n'a sa place que dans les rapports annuels.</t>
-  </si>
-  <si>
-    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
-  </si>
-  <si>
-    <t>Parce que les produits chimiques n'ont aucun lien avec la durabilité.</t>
+    <t>Parce que des objectifs environnementaux documentés créent surtout de la transparence, mais influencent peu les opérations.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD complètent les exigences légales par un cadre volontaire et remplacent en grande partie les contrôles juridiques.</t>
+  </si>
+  <si>
+    <t>Parce que, dans la chimie, la durabilité concerne surtout l'énergie utilisée en production, et non la distribution.</t>
   </si>
   <si>
     <t>Parce que les emballages, le recyclage et la responsabilité des fournisseurs peuvent influencer les performances en matière de durabilité.</t>
@@ -484,7 +500,7 @@
     <t>Quelle affirmation constitue une idée fausse courante au sujet de l'ODD 12 ?</t>
   </si>
   <si>
-    <t>Le recyclage à lui seul résout tous les problèmes de consommation.</t>
+    <t>Un recyclage systématique suffit à lui seul pour atteindre les principaux objectifs de l'ODD 12.</t>
   </si>
   <si>
     <t>L'ODD 12 peut être lié aux décisions quotidiennes.</t>
@@ -502,16 +518,16 @@
     <t>Quel comportement permet le mieux de passer de la théorie à l'action pour l'ODD 12 ?</t>
   </si>
   <si>
-    <t>Attendre que quelqu'un d'autre règle tout.</t>
-  </si>
-  <si>
-    <t>Choisir une amélioration concrète et la mener à bien.</t>
-  </si>
-  <si>
-    <t>Parler de durabilité sans rien changer.</t>
-  </si>
-  <si>
-    <t>Faire le contraire quand personne ne vérifie.</t>
+    <t>Attendre des normes sectorielles uniformes avant de lancer des améliorations individuelles.</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mettre en œuvre de manière cohérente.</t>
+  </si>
+  <si>
+    <t>Inscrire d'abord les objectifs dans des directives et reporter leur mise en œuvre à une période ultérieure.</t>
+  </si>
+  <si>
+    <t>Ne poursuivre que les améliorations dont les économies à court terme peuvent être démontrées avec certitude.</t>
   </si>
   <si>
     <t>Une action concrète favorise l'apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement pratique.</t>
@@ -520,16 +536,16 @@
     <t>Pourquoi l'ODD 12 est-il un sujet d'apprentissage utile pour les employés ?</t>
   </si>
   <si>
-    <t>Il n'a aucun rapport avec la culture d'entreprise.</t>
-  </si>
-  <si>
-    <t>Il supprime le besoin de connaissances spécialisées.</t>
+    <t>Il fournit des règles de conduite uniformes qui remplacent en grande partie le jugement individuel.</t>
+  </si>
+  <si>
+    <t>Il permet de prendre des décisions de durabilité sans tenir compte des connaissances spécialisées sur les risques et la réglementation.</t>
   </si>
   <si>
     <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
   </si>
   <si>
-    <t>Il fournit une réponse parfaite pour chaque situation.</t>
+    <t>Il fournit un catalogue fixe de mesures applicable de la même manière dans tous les services.</t>
   </si>
   <si>
     <t>L'apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et les choix familiers. Les ODD sont plus motivants lorsqu'ils semblent pertinents, concrets et liés aux rôles de chacun.</t>
@@ -538,13 +554,13 @@
     <t>Quelle quantité d'emballages réutilisables STOCKMEIER Chemie a-t-elle mise en circulation ?</t>
   </si>
   <si>
-    <t>Zéro tonne</t>
-  </si>
-  <si>
-    <t>Une seule palette</t>
-  </si>
-  <si>
-    <t>6,2 kilogrammes</t>
+    <t>625,54 tonnes</t>
+  </si>
+  <si>
+    <t>6 255,4 kilogrammes</t>
+  </si>
+  <si>
+    <t>62 554 tonnes</t>
   </si>
   <si>
     <t>6 255,4 tonnes</t>
@@ -562,13 +578,13 @@
     <t>Carton, palettes et films</t>
   </si>
   <si>
-    <t>Tous les déchets liquides dangereux</t>
-  </si>
-  <si>
-    <t>Uniquement les gobelets à café du bureau</t>
-  </si>
-  <si>
-    <t>Toutes les matières premières dans le monde</t>
+    <t>Verre, fûts métalliques et GRV</t>
+  </si>
+  <si>
+    <t>Carton, papier de bureau et bois</t>
+  </si>
+  <si>
+    <t>Films plastiques, bidons et fûts</t>
   </si>
   <si>
     <t>Le rapport indique que le carton, les palettes et les films sont recyclés à 100 %. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe s'inscrivent dans les objectifs mondiaux.</t>
@@ -577,16 +593,16 @@
     <t>Que montre l'exemple des clips de fût ?</t>
   </si>
   <si>
-    <t>Les déchets doivent toujours être ignorés.</t>
+    <t>La réutilisation est surtout rentable lorsque le transport de retour est organisé de manière centralisée.</t>
   </si>
   <si>
     <t>La pensée circulaire peut réduire les déchets et les nouveaux achats.</t>
   </si>
   <si>
-    <t>Les petits matériaux n'ont jamais d'importance.</t>
-  </si>
-  <si>
-    <t>La réutilisation entre sites est impossible.</t>
+    <t>Les petits matériaux ne devraient être pris en compte que lorsqu'ils représentent une part importante du poids des déchets.</t>
+  </si>
+  <si>
+    <t>La réutilisation entre sites exige des processus d'approvisionnement identiques.</t>
   </si>
   <si>
     <t>Le rapport décrit le retour de 650 clips de fût en vue de leur réutilisation, ce qui réduit la consommation de matériaux et les coûts. Les exemples de STOCKMEIER rendent l'ODD concret et montrent comment les initiatives du Groupe s'inscrivent dans les objectifs mondiaux.</t>
@@ -595,16 +611,16 @@
     <t>À la maison, quelle action soutient le mieux l'ODD 12 ?</t>
   </si>
   <si>
-    <t>Acheter plus que nécessaire</t>
-  </si>
-  <si>
-    <t>Jeter des produits encore utilisables</t>
-  </si>
-  <si>
-    <t>Réparer ou réutiliser des objets avant de les remplacer</t>
-  </si>
-  <si>
-    <t>Ignorer le tri des déchets</t>
+    <t>Choisir des produits à emballage recyclable, même s'ils doivent être remplacés plus tôt.</t>
+  </si>
+  <si>
+    <t>Remplacer les appareils anciens mais fonctionnels dès qu'une version plus efficace apparaît.</t>
+  </si>
+  <si>
+    <t>Réparer ou réutiliser des objets avant de les remplacer.</t>
+  </si>
+  <si>
+    <t>Acheter en grand format pour réduire l'emballage par unité, même si une partie reste inutilisée.</t>
   </si>
   <si>
     <t>La réutilisation et la réparation réduisent la demande en ressources. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu'ils sont répétés par beaucoup de personnes.</t>
@@ -613,16 +629,16 @@
     <t>Quelle habitude d'achat favorise une consommation responsable ?</t>
   </si>
   <si>
-    <t>Ignorer la durée de vie des produits</t>
-  </si>
-  <si>
-    <t>Acheter des doublons sans nécessité</t>
-  </si>
-  <si>
-    <t>Choisir systématiquement des emballages excessifs</t>
-  </si>
-  <si>
-    <t>Planifier ses achats pour éviter le gaspillage</t>
+    <t>Toujours choisir le produit le moins cher, même si sa durée de vie est plus courte.</t>
+  </si>
+  <si>
+    <t>Acheter des produits en promotion sans vérifier les stocks existants.</t>
+  </si>
+  <si>
+    <t>Retenir l'emballage recyclable comme seul critère, quelle que soit la quantité nécessaire.</t>
+  </si>
+  <si>
+    <t>Planifier ses achats pour éviter le gaspillage.</t>
   </si>
   <si>
     <t>La planification réduit la consommation inutile et les déchets. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu'ils sont répétés par beaucoup de personnes.</t>
@@ -634,16 +650,16 @@
     <t>Leicht · Einfachauswahl</t>
   </si>
   <si>
-    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
-  </si>
-  <si>
-    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+    <t>Es geht vorrangig darum, einzelne Produktionsschritte effizienter zu machen, unabhängig vom Konsumverhalten.</t>
+  </si>
+  <si>
+    <t>Es fördert vor allem die freiwillige Kommunikation über nachhaltige Produkte, ohne die Ressourcennutzung einzubeziehen.</t>
   </si>
   <si>
     <t>Es konzentriert sich auf den verantwortungsvollen Umgang mit Ressourcen und Kreislaufwirtschaft.</t>
   </si>
   <si>
-    <t>Es gilt nur für nationale Regierungen.</t>
+    <t>Es zielt hauptsächlich auf den Ausbau von Recyclingkapazitäten; andere Phasen des Produktlebenszyklus sind nachrangig.</t>
   </si>
   <si>
     <t>Bei SDG 12 geht es um den verantwortungsvollen Umgang mit Ressourcen und Kreislaufwirtschaft sowie darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 12 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übertragen.</t>
@@ -655,13 +671,13 @@
     <t>Mittel · Einfachauswahl</t>
   </si>
   <si>
-    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
-  </si>
-  <si>
-    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
-  </si>
-  <si>
-    <t>Weil Chemikalien nichts mit Nachhaltigkeit zu tun haben.</t>
+    <t>Weil dokumentierte Umweltziele vor allem Transparenz schaffen, operative Abläufe jedoch kaum beeinflussen.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs gesetzliche Anforderungen als freiwilliger Rahmen ergänzen und rechtliche Prüfungen weitgehend ersetzen.</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit in der Chemie vor allem den Energieverbrauch der Produktion betrifft, nicht aber die Distribution.</t>
   </si>
   <si>
     <t>Weil Verpackungen, Recycling und Lieferantenverantwortung die Nachhaltigkeitsleistung beeinflussen können.</t>
@@ -673,7 +689,7 @@
     <t>Welche Aussage ist ein verbreitetes Missverständnis über SDG 12?</t>
   </si>
   <si>
-    <t>Recycling allein löst alle Konsumprobleme.</t>
+    <t>Konsequentes Recycling allein reicht aus, um die wesentlichen Ziele von SDG 12 zu erreichen.</t>
   </si>
   <si>
     <t>SDG 12 kann mit täglichen Entscheidungen verknüpft werden.</t>
@@ -691,16 +707,16 @@
     <t>Welches Verhalten setzt SDG 12 am besten von der Theorie in die Praxis um?</t>
   </si>
   <si>
-    <t>Warten, bis jemand anderes alles löst.</t>
+    <t>Erst branchenweit einheitliche Standards abwarten, bevor einzelne Verbesserungen begonnen werden.</t>
   </si>
   <si>
     <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
   </si>
   <si>
-    <t>Über Nachhaltigkeit sprechen, aber nichts ändern.</t>
-  </si>
-  <si>
-    <t>Das Gegenteil tun, wenn niemand hinsieht.</t>
+    <t>Ziele zunächst in Leitlinien festhalten und die Umsetzung auf eine spätere Berichtsperiode verschieben.</t>
+  </si>
+  <si>
+    <t>Verbesserungen nur dort verfolgen, wo kurzfristige Kosteneinsparungen sicher nachweisbar sind.</t>
   </si>
   <si>
     <t>Konkretes Handeln schafft Lernerfahrungen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu praktischen Verhaltensänderungen führen.</t>
@@ -709,16 +725,16 @@
     <t>Was macht SDG 12 zu einem nützlichen Lernthema für Mitarbeitende?</t>
   </si>
   <si>
-    <t>Es hat nichts mit der Unternehmenskultur zu tun.</t>
-  </si>
-  <si>
-    <t>Es macht Fachwissen überflüssig.</t>
+    <t>Es vermittelt einheitliche Verhaltensregeln, die individuelle Abwägungen weitgehend ersetzen.</t>
+  </si>
+  <si>
+    <t>Es ermöglicht Nachhaltigkeitsentscheidungen, ohne Fachwissen zu Risiken und Vorschriften einzubeziehen.</t>
   </si>
   <si>
     <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen bei der Arbeit und zu Hause kennen.</t>
   </si>
   <si>
-    <t>Es liefert für jede Situation eine perfekte Antwort.</t>
+    <t>Es bietet einen festen Maßnahmenkatalog, der in allen Unternehmensbereichen gleich angewandt werden kann.</t>
   </si>
   <si>
     <t>Am meisten lernen Menschen, wenn sie den Zusammenhang zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind besonders ansprechend, wenn sie relevant, konkret und mit den Rollen der Menschen verbunden sind.</t>
@@ -727,13 +743,13 @@
     <t>Wie viele Mehrwegverpackungen brachte STOCKMEIER Chemie in Umlauf?</t>
   </si>
   <si>
-    <t>Null Tonnen</t>
-  </si>
-  <si>
-    <t>Nur eine Palette</t>
-  </si>
-  <si>
-    <t>6,2 Kilogramm</t>
+    <t>625,54 Tonnen</t>
+  </si>
+  <si>
+    <t>6.255,4 Kilogramm</t>
+  </si>
+  <si>
+    <t>62.554 Tonnen</t>
   </si>
   <si>
     <t>6.255,4 Tonnen</t>
@@ -751,13 +767,13 @@
     <t>Karton, Paletten und Folien</t>
   </si>
   <si>
-    <t>Alle gefährlichen flüssigen Abfälle</t>
-  </si>
-  <si>
-    <t>Nur Kaffeebecher im Büro</t>
-  </si>
-  <si>
-    <t>Alle Rohstoffe weltweit</t>
+    <t>Glas, Metallfässer und IBC-Behälter</t>
+  </si>
+  <si>
+    <t>Karton, Büropapier und Holz</t>
+  </si>
+  <si>
+    <t>Kunststofffolien, Kanister und Fässer</t>
   </si>
   <si>
     <t>Der Bericht nennt Karton, Paletten und Folien als zu 100 % recycelt. Die Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
@@ -766,16 +782,16 @@
     <t>Was zeigt das Beispiel mit den Fassclips?</t>
   </si>
   <si>
-    <t>Abfall sollte immer ignoriert werden.</t>
+    <t>Wiederverwendung lohnt sich vor allem, wenn der Rücktransport zentral organisiert wird.</t>
   </si>
   <si>
     <t>Kreislauforientiertes Denken kann Abfall und Neukäufe reduzieren.</t>
   </si>
   <si>
-    <t>Kleine Materialien spielen nie eine Rolle.</t>
-  </si>
-  <si>
-    <t>Wiederverwendung über verschiedene Standorte hinweg ist unmöglich.</t>
+    <t>Kleine Materialien sollten erst berücksichtigt werden, wenn sie einen großen Gewichtsanteil am Abfall haben.</t>
+  </si>
+  <si>
+    <t>Standortübergreifende Wiederverwendung setzt identische Beschaffungsprozesse voraus.</t>
   </si>
   <si>
     <t>Der Bericht beschreibt, dass 650 Fassclips zur Wiederverwendung zurückgegeben wurden, wodurch Materialverbrauch und Kosten sinken. Die Beispiele von STOCKMEIER machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
@@ -784,16 +800,16 @@
     <t>Welche Handlung zu Hause unterstützt SDG 12 am besten?</t>
   </si>
   <si>
-    <t>Mehr kaufen als nötig</t>
-  </si>
-  <si>
-    <t>Noch verwendbare Produkte wegwerfen</t>
-  </si>
-  <si>
-    <t>Gegenstände reparieren oder wiederverwenden, bevor sie ersetzt werden</t>
-  </si>
-  <si>
-    <t>Mülltrennung ignorieren</t>
+    <t>Produkte mit recycelbarer Verpackung wählen, auch wenn sie dadurch früher ersetzt werden müssen.</t>
+  </si>
+  <si>
+    <t>Ältere, noch funktionsfähige Geräte bei jeder effizienteren Neuauflage austauschen.</t>
+  </si>
+  <si>
+    <t>Gegenstände reparieren oder wiederverwenden, bevor sie ersetzt werden.</t>
+  </si>
+  <si>
+    <t>Großpackungen kaufen, um Verpackung je Einheit zu sparen, auch wenn ein Teil ungenutzt bleibt.</t>
   </si>
   <si>
     <t>Wiederverwendung und Reparatur senken den Ressourcenbedarf. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
@@ -802,16 +818,16 @@
     <t>Welche Einkaufsgewohnheit unterstützt verantwortungsvollen Konsum?</t>
   </si>
   <si>
-    <t>Die Lebensdauer von Produkten ignorieren</t>
-  </si>
-  <si>
-    <t>Ohne Bedarf doppelte Produkte kaufen</t>
-  </si>
-  <si>
-    <t>Jedes Mal übermäßig viel Verpackung wählen</t>
-  </si>
-  <si>
-    <t>Einkäufe planen, um Verschwendung zu vermeiden</t>
+    <t>Grundsätzlich das günstigste Produkt wählen, auch wenn seine Lebensdauer kürzer ist.</t>
+  </si>
+  <si>
+    <t>Reduzierte Produkte auf Vorrat kaufen, ohne den vorhandenen Bestand zu prüfen.</t>
+  </si>
+  <si>
+    <t>Recyclingfähige Verpackung als einziges Kriterium nutzen, unabhängig von der benötigten Menge.</t>
+  </si>
+  <si>
+    <t>Einkäufe planen, um Verschwendung zu vermeiden.</t>
   </si>
   <si>
     <t>Planung reduziert unnötigen Konsum und Abfall. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
@@ -823,16 +839,16 @@
     <t>Fácil · Opción única</t>
   </si>
   <si>
-    <t>Pide a las empresas que ignoren los impactos a largo plazo.</t>
-  </si>
-  <si>
-    <t>Es solo un eslogan de marketing sin significado práctico.</t>
+    <t>Busca principalmente hacer más eficientes ciertas etapas de producción, independientemente de los hábitos de consumo.</t>
+  </si>
+  <si>
+    <t>Promueve sobre todo la comunicación voluntaria sobre productos sostenibles, sin abordar el uso de recursos.</t>
   </si>
   <si>
     <t>Se centra en el uso responsable de los recursos y la circularidad.</t>
   </si>
   <si>
-    <t>Solo se aplica a los gobiernos nacionales.</t>
+    <t>Su objetivo principal es ampliar la capacidad de reciclaje; las demás fases del ciclo de vida son secundarias.</t>
   </si>
   <si>
     <t>El ODS 12 trata del uso responsable de los recursos y la circularidad, y de convertir ese objetivo en acciones concretas. El ODS 12 resulta útil cuando las personas traducen el objetivo general en decisiones prácticas.</t>
@@ -844,13 +860,13 @@
     <t>Intermedio · Opción única</t>
   </si>
   <si>
-    <t>Porque la sostenibilidad solo corresponde a los informes anuales.</t>
-  </si>
-  <si>
-    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
-  </si>
-  <si>
-    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+    <t>Porque los objetivos ambientales documentados generan sobre todo transparencia, pero apenas influyen en las operaciones.</t>
+  </si>
+  <si>
+    <t>Porque los ODS complementan los requisitos legales como marco voluntario y sustituyen en gran medida las revisiones jurídicas.</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad en la industria química se refiere principalmente al uso de energía en producción, no a la distribución.</t>
   </si>
   <si>
     <t>Porque los envases, el reciclaje y la responsabilidad de los proveedores pueden influir en el desempeño de sostenibilidad.</t>
@@ -862,7 +878,7 @@
     <t>¿Qué afirmación es un malentendido común sobre el ODS 12?</t>
   </si>
   <si>
-    <t>El reciclaje por sí solo resuelve todos los problemas de consumo.</t>
+    <t>El reciclaje sistemático por sí solo basta para alcanzar los principales objetivos del ODS 12.</t>
   </si>
   <si>
     <t>El ODS 12 puede vincularse con las decisiones diarias.</t>
@@ -880,16 +896,16 @@
     <t>¿Qué comportamiento convierte mejor el ODS 12 de la teoría en acción?</t>
   </si>
   <si>
-    <t>Esperar a que otra persona lo arregle todo.</t>
-  </si>
-  <si>
-    <t>Elegir una mejora concreta y llevarla a cabo.</t>
-  </si>
-  <si>
-    <t>Hablar de sostenibilidad sin cambiar nada.</t>
-  </si>
-  <si>
-    <t>Hacer lo contrario cuando nadie está mirando.</t>
+    <t>Esperar a que existan normas sectoriales uniformes antes de iniciar mejoras individuales.</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y aplicarla de forma coherente.</t>
+  </si>
+  <si>
+    <t>Registrar primero los objetivos en directrices y aplazar la aplicación a un periodo posterior.</t>
+  </si>
+  <si>
+    <t>Aplicar mejoras solo cuando puedan demostrarse con certeza ahorros de costes a corto plazo.</t>
   </si>
   <si>
     <t>La acción concreta genera aprendizaje y mejoras medibles. La concienciación sobre la sostenibilidad debe conducir a un cambio práctico de comportamiento.</t>
@@ -898,16 +914,16 @@
     <t>¿Qué hace que el ODS 12 sea un tema de aprendizaje útil para los empleados?</t>
   </si>
   <si>
-    <t>No está relacionado con la cultura empresarial.</t>
-  </si>
-  <si>
-    <t>Elimina la necesidad de conocimientos especializados.</t>
+    <t>Ofrece reglas de conducta uniformes que sustituyen en gran medida el criterio individual.</t>
+  </si>
+  <si>
+    <t>Permite tomar decisiones de sostenibilidad sin considerar conocimientos especializados sobre riesgos y normativa.</t>
   </si>
   <si>
     <t>Vincula los retos mundiales con decisiones que las personas reconocen en el trabajo y en casa.</t>
   </si>
   <si>
-    <t>Ofrece una respuesta perfecta para cada situación.</t>
+    <t>Ofrece un catálogo fijo de medidas aplicable por igual en todas las áreas de la empresa.</t>
   </si>
   <si>
     <t>El aprendizaje más sólido se produce cuando las personas ven la conexión entre los objetivos mundiales y las decisiones cotidianas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y relacionados con las funciones de las personas.</t>
@@ -916,13 +932,13 @@
     <t>¿Cuántos envases reutilizables puso en circulación STOCKMEIER Chemie?</t>
   </si>
   <si>
-    <t>Cero toneladas</t>
-  </si>
-  <si>
-    <t>Solo un palé</t>
-  </si>
-  <si>
-    <t>6,2 kilogramos</t>
+    <t>625,54 toneladas</t>
+  </si>
+  <si>
+    <t>6.255,4 kilogramos</t>
+  </si>
+  <si>
+    <t>62.554 toneladas</t>
   </si>
   <si>
     <t>6.255,4 toneladas</t>
@@ -940,13 +956,13 @@
     <t>Cartón, palés y films</t>
   </si>
   <si>
-    <t>Todos los residuos líquidos peligrosos</t>
-  </si>
-  <si>
-    <t>Solo los vasos de café de la oficina</t>
-  </si>
-  <si>
-    <t>Todas las materias primas del mundo</t>
+    <t>Vidrio, bidones metálicos e IBC</t>
+  </si>
+  <si>
+    <t>Cartón, papel de oficina y madera</t>
+  </si>
+  <si>
+    <t>Films de plástico, garrafas y bidones</t>
   </si>
   <si>
     <t>El informe indica que el cartón, los palés y los films se reciclan al 100 %. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos mundiales.</t>
@@ -955,16 +971,16 @@
     <t>¿Qué demuestra el ejemplo de los clips para bidones?</t>
   </si>
   <si>
-    <t>Los residuos siempre deben ignorarse.</t>
+    <t>La reutilización resulta más rentable cuando el transporte de retorno se organiza de forma centralizada.</t>
   </si>
   <si>
     <t>El pensamiento circular puede reducir los residuos y las nuevas compras.</t>
   </si>
   <si>
-    <t>Los materiales pequeños nunca importan.</t>
-  </si>
-  <si>
-    <t>La reutilización entre centros es imposible.</t>
+    <t>Los materiales pequeños solo deberían considerarse cuando representan una gran proporción del peso de los residuos.</t>
+  </si>
+  <si>
+    <t>La reutilización entre centros requiere procesos de compra idénticos.</t>
   </si>
   <si>
     <t>El informe describe la devolución de 650 clips para bidones para su reutilización, lo que reduce el consumo de materiales y los costes. Los ejemplos de STOCKMEIER hacen que el ODS sea concreto y muestran cómo las iniciativas del Grupo se conectan con los objetivos mundiales.</t>
@@ -973,16 +989,16 @@
     <t>En casa, ¿qué acción apoya mejor el ODS 12?</t>
   </si>
   <si>
-    <t>Comprar más de lo necesario</t>
-  </si>
-  <si>
-    <t>Tirar productos que todavía se pueden usar</t>
-  </si>
-  <si>
-    <t>Reparar o reutilizar objetos antes de sustituirlos</t>
-  </si>
-  <si>
-    <t>Ignorar la separación de residuos</t>
+    <t>Elegir productos con envases reciclables aunque deban sustituirse antes.</t>
+  </si>
+  <si>
+    <t>Sustituir aparatos antiguos pero funcionales cada vez que aparezca una versión más eficiente.</t>
+  </si>
+  <si>
+    <t>Reparar o reutilizar objetos antes de sustituirlos.</t>
+  </si>
+  <si>
+    <t>Comprar formatos grandes para reducir el envase por unidad, aunque una parte quede sin usar.</t>
   </si>
   <si>
     <t>La reutilización y la reparación reducen la demanda de recursos. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
@@ -991,37 +1007,226 @@
     <t>¿Qué hábito de compra favorece el consumo responsable?</t>
   </si>
   <si>
-    <t>Ignorar la vida útil del producto</t>
-  </si>
-  <si>
-    <t>Comprar productos duplicados sin necesidad</t>
-  </si>
-  <si>
-    <t>Elegir siempre un embalaje excesivo</t>
-  </si>
-  <si>
-    <t>Planificar las compras para evitar el desperdicio</t>
+    <t>Elegir siempre el producto más barato, aunque tenga una vida útil más corta.</t>
+  </si>
+  <si>
+    <t>Comprar productos rebajados para almacenarlos sin comprobar las existencias.</t>
+  </si>
+  <si>
+    <t>Usar el envase reciclable como único criterio, independientemente de la cantidad necesaria.</t>
+  </si>
+  <si>
+    <t>Planificar las compras para evitar el desperdicio.</t>
   </si>
   <si>
     <t>La planificación reduce el consumo innecesario y los residuos. Los hábitos personales importan porque muchas pequeñas decisiones adquieren importancia cuando muchas personas las repiten.</t>
   </si>
   <si>
+    <t>Qual è l'idea principale dell'OSS 12 – Consumo e produzione responsabili?</t>
+  </si>
+  <si>
+    <t>Facile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Mira soprattutto a rendere più efficienti singole fasi produttive, indipendentemente dalle abitudini di consumo.</t>
+  </si>
+  <si>
+    <t>Promuove principalmente la comunicazione volontaria sui prodotti sostenibili, senza considerare l'uso delle risorse.</t>
+  </si>
+  <si>
+    <t>Si concentra sull'uso responsabile delle risorse e sulla circolarità.</t>
+  </si>
+  <si>
+    <t>Punta soprattutto ad ampliare la capacità di riciclaggio; le altre fasi del ciclo di vita sono secondarie.</t>
+  </si>
+  <si>
+    <t>L'OSS 12 riguarda l'uso responsabile delle risorse e la circolarità e la trasformazione di questo obiettivo in azioni concrete. L'OSS 12 diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Perché l'OSS 12 è rilevante per un'azienda di distribuzione e produzione di prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Media · Scelta singola</t>
+  </si>
+  <si>
+    <t>Perché gli obiettivi ambientali documentati creano soprattutto trasparenza, ma incidono poco sulle attività operative.</t>
+  </si>
+  <si>
+    <t>Perché gli OSS integrano i requisiti di legge come quadro volontario e sostituiscono in gran parte le verifiche legali.</t>
+  </si>
+  <si>
+    <t>Perché nella chimica la sostenibilità riguarda soprattutto l'energia usata in produzione, non la distribuzione.</t>
+  </si>
+  <si>
+    <t>Perché gli imballaggi, il riciclaggio e la responsabilità dei fornitori possono influire sulle prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Gli imballaggi, il riciclaggio e la responsabilità dei fornitori sono ambiti concreti in cui un'azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull'OSS 12?</t>
+  </si>
+  <si>
+    <t>Il riciclaggio sistematico da solo è sufficiente per raggiungere i principali obiettivi dell'OSS 12.</t>
+  </si>
+  <si>
+    <t>L'OSS 12 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo la portata dell'OSS e nasconde opportunità pratiche. Una buona domanda a quiz spesso mette in discussione un'idea errata, perché rende l'apprendimento memorabile.</t>
+  </si>
+  <si>
+    <t>Quale comportamento traduce meglio l'OSS 12 dalla teoria all'azione?</t>
+  </si>
+  <si>
+    <t>Attendere standard uniformi di settore prima di avviare singoli miglioramenti.</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e attuarlo con coerenza.</t>
+  </si>
+  <si>
+    <t>Inserire prima gli obiettivi nelle linee guida e rinviarne l'attuazione a un periodo successivo.</t>
+  </si>
+  <si>
+    <t>Perseguire miglioramenti solo quando i risparmi a breve termine sono dimostrabili con certezza.</t>
+  </si>
+  <si>
+    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico dei comportamenti.</t>
+  </si>
+  <si>
+    <t>Cosa rende l'OSS 12 un tema di apprendimento utile per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Fornisce regole di comportamento uniformi che sostituiscono in gran parte la valutazione individuale.</t>
+  </si>
+  <si>
+    <t>Consente decisioni di sostenibilità senza considerare conoscenze specialistiche su rischi e normative.</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Fornisce un catalogo fisso di misure applicabile allo stesso modo in tutte le aree aziendali.</t>
+  </si>
+  <si>
+    <t>L'apprendimento più efficace avviene quando le persone vedono il legame tra obiettivi globali e scelte familiari. Gli OSS sono più coinvolgenti quando risultano pertinenti, concreti e connessi ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Quanti imballaggi riutilizzabili ha immesso in circolazione STOCKMEIER Chemie?</t>
+  </si>
+  <si>
+    <t>625,54 tonnellate</t>
+  </si>
+  <si>
+    <t>6.255,4 chilogrammi</t>
+  </si>
+  <si>
+    <t>62.554 tonnellate</t>
+  </si>
+  <si>
+    <t>6.255,4 tonnellate</t>
+  </si>
+  <si>
+    <t>Il rapporto indica 6.255,4 tonnellate di imballaggi riutilizzabili. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quali materiali risultano riciclati al 100%?</t>
+  </si>
+  <si>
+    <t>Difficile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Cartone, pallet e pellicole</t>
+  </si>
+  <si>
+    <t>Vetro, fusti metallici e IBC</t>
+  </si>
+  <si>
+    <t>Cartone, carta da ufficio e legno</t>
+  </si>
+  <si>
+    <t>Pellicole di plastica, taniche e fusti</t>
+  </si>
+  <si>
+    <t>Il rapporto indica che cartone, pallet e pellicole sono riciclati al 100%. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Che cosa dimostra l'esempio delle clip per fusti?</t>
+  </si>
+  <si>
+    <t>Il riutilizzo è particolarmente conveniente quando il trasporto di ritorno è organizzato centralmente.</t>
+  </si>
+  <si>
+    <t>Il pensiero circolare può ridurre i rifiuti e i nuovi acquisti.</t>
+  </si>
+  <si>
+    <t>I materiali piccoli dovrebbero essere considerati solo quando rappresentano una quota elevata del peso dei rifiuti.</t>
+  </si>
+  <si>
+    <t>Il riutilizzo tra sedi richiede processi di approvvigionamento identici.</t>
+  </si>
+  <si>
+    <t>Il rapporto descrive la restituzione di 650 clip per fusti destinate al riutilizzo, riducendo il consumo di materiali e i costi. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>A casa, quale azione sostiene meglio l'OSS 12?</t>
+  </si>
+  <si>
+    <t>Scegliere prodotti con imballaggi riciclabili anche se devono essere sostituiti prima.</t>
+  </si>
+  <si>
+    <t>Sostituire apparecchi vecchi ma funzionanti ogni volta che esce una versione più efficiente.</t>
+  </si>
+  <si>
+    <t>Riparare o riutilizzare gli oggetti prima di sostituirli.</t>
+  </si>
+  <si>
+    <t>Acquistare confezioni grandi per ridurre l'imballaggio per unità, anche se una parte resta inutilizzata.</t>
+  </si>
+  <si>
+    <t>Il riutilizzo e la riparazione riducono la domanda di risorse. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Quale abitudine di acquisto favorisce il consumo responsabile?</t>
+  </si>
+  <si>
+    <t>Scegliere sempre il prodotto meno costoso, anche se dura meno.</t>
+  </si>
+  <si>
+    <t>Fare scorta di prodotti scontati senza controllare le scorte esistenti.</t>
+  </si>
+  <si>
+    <t>Usare l'imballaggio riciclabile come unico criterio, indipendentemente dalla quantità necessaria.</t>
+  </si>
+  <si>
+    <t>Pianificare gli acquisti per evitare sprechi.</t>
+  </si>
+  <si>
+    <t>La pianificazione riduce i consumi inutili e i rifiuti. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
     <t>Jaka jest główna idea Celu Zrównoważonego Rozwoju 12 – Odpowiedzialna konsumpcja i produkcja?</t>
   </si>
   <si>
     <t>Łatwe · Jednokrotny wybór</t>
   </si>
   <si>
-    <t>Wzywa firmy do ignorowania długoterminowych skutków.</t>
-  </si>
-  <si>
-    <t>To tylko slogan marketingowy bez praktycznego znaczenia.</t>
+    <t>Chodzi przede wszystkim o zwiększanie efektywności poszczególnych etapów produkcji, niezależnie od wzorców konsumpcji.</t>
+  </si>
+  <si>
+    <t>Promuje głównie dobrowolne informowanie o zrównoważonych produktach, bez uwzględniania wykorzystania zasobów.</t>
   </si>
   <si>
     <t>Koncentruje się na odpowiedzialnym wykorzystaniu zasobów i obiegu zamkniętym.</t>
   </si>
   <si>
-    <t>Dotyczy wyłącznie rządów krajowych.</t>
+    <t>Jego głównym celem jest rozwój zdolności recyklingu; pozostałe etapy cyklu życia produktu są drugorzędne.</t>
   </si>
   <si>
     <t>Cel 12 dotyczy odpowiedzialnego wykorzystania zasobów i obiegu zamkniętego oraz przekładania tego celu na konkretne działania. Cel 12 staje się użyteczny, gdy ludzie przekładają ogólny cel na praktyczne decyzje.</t>
@@ -1033,13 +1238,13 @@
     <t>Średnie · Jednokrotny wybór</t>
   </si>
   <si>
-    <t>Ponieważ zrównoważony rozwój powinien pojawiać się wyłącznie w raportach rocznych.</t>
-  </si>
-  <si>
-    <t>Ponieważ Cele Zrównoważonego Rozwoju zastępują wszystkie wymogi prawne.</t>
-  </si>
-  <si>
-    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+    <t>Ponieważ udokumentowane cele środowiskowe przede wszystkim zwiększają przejrzystość, ale mają niewielki wpływ na działalność operacyjną.</t>
+  </si>
+  <si>
+    <t>Ponieważ Cele uzupełniają wymogi prawne jako dobrowolne ramy i w dużej mierze zastępują kontrole prawne.</t>
+  </si>
+  <si>
+    <t>Ponieważ w branży chemicznej zrównoważony rozwój dotyczy głównie zużycia energii w produkcji, a nie dystrybucji.</t>
   </si>
   <si>
     <t>Ponieważ opakowania, recykling i odpowiedzialność dostawców mogą wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
@@ -1051,7 +1256,7 @@
     <t>Które stwierdzenie jest częstym nieporozumieniem dotyczącym Celu 12?</t>
   </si>
   <si>
-    <t>Sam recykling rozwiązuje wszystkie problemy związane z konsumpcją.</t>
+    <t>Systematyczny recykling sam w sobie wystarcza do osiągnięcia głównych założeń Celu 12.</t>
   </si>
   <si>
     <t>Cel 12 można powiązać z codziennymi decyzjami.</t>
@@ -1069,16 +1274,16 @@
     <t>Które zachowanie najlepiej przekłada Cel 12 z teorii na działanie?</t>
   </si>
   <si>
-    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
-  </si>
-  <si>
-    <t>Wybranie konkretnego usprawnienia i konsekwentne wdrożenie go.</t>
-  </si>
-  <si>
-    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
-  </si>
-  <si>
-    <t>Robienie czegoś przeciwnego, gdy nikt nie sprawdza.</t>
+    <t>Poczekać na jednolite standardy branżowe przed rozpoczęciem pojedynczych usprawnień.</t>
+  </si>
+  <si>
+    <t>Wybrać konkretne usprawnienie i konsekwentnie je wdrożyć.</t>
+  </si>
+  <si>
+    <t>Najpierw zapisać cele w wytycznych, a wdrożenie odłożyć na późniejszy okres sprawozdawczy.</t>
+  </si>
+  <si>
+    <t>Realizować tylko te usprawnienia, dla których można z pewnością wykazać krótkoterminowe oszczędności.</t>
   </si>
   <si>
     <t>Konkretne działanie umożliwia naukę i mierzalną poprawę. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowań.</t>
@@ -1087,16 +1292,16 @@
     <t>Dlaczego Cel 12 jest wartościowym tematem edukacyjnym dla pracowników?</t>
   </si>
   <si>
-    <t>Nie ma związku z kulturą firmy.</t>
-  </si>
-  <si>
-    <t>Eliminuje potrzebę wiedzy eksperckiej.</t>
+    <t>Przekazuje jednolite zasady postępowania, które w dużej mierze zastępują indywidualną ocenę.</t>
+  </si>
+  <si>
+    <t>Umożliwia podejmowanie decyzji bez uwzględniania specjalistycznej wiedzy o ryzyku i przepisach.</t>
   </si>
   <si>
     <t>Łączy globalne wyzwania z wyborami znanymi ludziom z pracy i domu.</t>
   </si>
   <si>
-    <t>Daje jedną idealną odpowiedź w każdej sytuacji.</t>
+    <t>Oferuje stały katalog działań, który można jednakowo stosować we wszystkich obszarach firmy.</t>
   </si>
   <si>
     <t>Najskuteczniejsza nauka ma miejsce wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi wyborami. Cele Zrównoważonego Rozwoju są najbardziej angażujące, gdy są istotne, konkretne i powiązane z rolami ludzi.</t>
@@ -1105,13 +1310,13 @@
     <t>Ile opakowań wielokrotnego użytku wprowadziła do obiegu firma STOCKMEIER Chemie?</t>
   </si>
   <si>
-    <t>Zero ton</t>
-  </si>
-  <si>
-    <t>Tylko jedną paletę</t>
-  </si>
-  <si>
-    <t>6,2 kilograma</t>
+    <t>625,54 tony</t>
+  </si>
+  <si>
+    <t>6 255,4 kilograma</t>
+  </si>
+  <si>
+    <t>62 554 tony</t>
   </si>
   <si>
     <t>6 255,4 tony</t>
@@ -1129,13 +1334,13 @@
     <t>Karton, palety i folie</t>
   </si>
   <si>
-    <t>Wszystkie niebezpieczne odpady płynne</t>
-  </si>
-  <si>
-    <t>Tylko kubki do kawy w biurze</t>
-  </si>
-  <si>
-    <t>Wszystkie surowce na świecie</t>
+    <t>Szkło, metalowe beczki i pojemniki IBC</t>
+  </si>
+  <si>
+    <t>Karton, papier biurowy i drewno</t>
+  </si>
+  <si>
+    <t>Folie z tworzyw sztucznych, kanistry i beczki</t>
   </si>
   <si>
     <t>W raporcie podano, że karton, palety i folie są w 100% poddawane recyklingowi. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z celami globalnymi.</t>
@@ -1144,16 +1349,16 @@
     <t>Co pokazuje przykład klipsów do beczek?</t>
   </si>
   <si>
-    <t>Odpady należy zawsze ignorować.</t>
+    <t>Ponowne użycie opłaca się przede wszystkim wtedy, gdy transport zwrotny jest organizowany centralnie.</t>
   </si>
   <si>
     <t>Myślenie cyrkularne może ograniczyć ilość odpadów i nowych zakupów.</t>
   </si>
   <si>
-    <t>Drobne materiały nigdy nie mają znaczenia.</t>
-  </si>
-  <si>
-    <t>Ponowne użycie w różnych lokalizacjach jest niemożliwe.</t>
+    <t>Drobne materiały należy uwzględniać dopiero wtedy, gdy stanowią znaczną część masy odpadów.</t>
+  </si>
+  <si>
+    <t>Ponowne użycie w różnych lokalizacjach wymaga identycznych procesów zakupowych.</t>
   </si>
   <si>
     <t>Raport opisuje zwrot 650 klipsów do beczek w celu ponownego użycia, co zmniejsza zużycie materiałów i koszty. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z celami globalnymi.</t>
@@ -1162,16 +1367,16 @@
     <t>Które działanie w domu najlepiej wspiera Cel 12?</t>
   </si>
   <si>
-    <t>Kupowanie więcej, niż potrzeba</t>
-  </si>
-  <si>
-    <t>Wyrzucanie produktów, których nadal można używać</t>
-  </si>
-  <si>
-    <t>Naprawianie lub ponowne używanie przedmiotów przed ich wymianą</t>
-  </si>
-  <si>
-    <t>Ignorowanie segregacji odpadów</t>
+    <t>Wybierać produkty w opakowaniach nadających się do recyklingu, nawet jeśli trzeba je wcześniej wymienić.</t>
+  </si>
+  <si>
+    <t>Wymieniać starsze, ale sprawne urządzenia za każdym razem, gdy pojawia się wydajniejsza wersja.</t>
+  </si>
+  <si>
+    <t>Naprawiać lub ponownie używać przedmiotów przed ich wymianą.</t>
+  </si>
+  <si>
+    <t>Kupować duże opakowania, aby zmniejszyć ilość opakowania na jednostkę, nawet jeśli część produktu pozostanie niewykorzystana.</t>
   </si>
   <si>
     <t>Ponowne użycie i naprawa zmniejszają zapotrzebowanie na zasoby. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy powtarza je wiele osób.</t>
@@ -1180,215 +1385,26 @@
     <t>Który nawyk zakupowy wspiera odpowiedzialną konsumpcję?</t>
   </si>
   <si>
-    <t>Ignorowanie okresu użytkowania produktu</t>
-  </si>
-  <si>
-    <t>Kupowanie niepotrzebnych duplikatów</t>
-  </si>
-  <si>
-    <t>Wybieranie za każdym razem nadmiernej ilości opakowań</t>
-  </si>
-  <si>
-    <t>Planowanie zakupów, aby uniknąć marnotrawstwa</t>
+    <t>Zawsze wybierać najtańszy produkt, nawet jeśli ma krótszy okres użytkowania.</t>
+  </si>
+  <si>
+    <t>Kupować przecenione produkty na zapas bez sprawdzenia posiadanych zasobów.</t>
+  </si>
+  <si>
+    <t>Traktować opakowanie nadające się do recyklingu jako jedyne kryterium, niezależnie od potrzebnej ilości.</t>
+  </si>
+  <si>
+    <t>Planować zakupy, aby uniknąć marnotrawstwa.</t>
   </si>
   <si>
     <t>Planowanie ogranicza niepotrzebną konsumpcję i odpady. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy powtarza je wiele osób.</t>
-  </si>
-  <si>
-    <t>Qual è l'idea principale dell'OSS 12 – Consumo e produzione responsabili?</t>
-  </si>
-  <si>
-    <t>Facile · Scelta singola</t>
-  </si>
-  <si>
-    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
-  </si>
-  <si>
-    <t>È solo uno slogan di marketing senza significato pratico.</t>
-  </si>
-  <si>
-    <t>Si concentra sull'uso responsabile delle risorse e sulla circolarità.</t>
-  </si>
-  <si>
-    <t>Si applica solo ai governi nazionali.</t>
-  </si>
-  <si>
-    <t>L'OSS 12 riguarda l'uso responsabile delle risorse e la circolarità e la trasformazione di questo obiettivo in azioni concrete. L'OSS 12 diventa utile quando le persone traducono l'obiettivo generale in decisioni pratiche.</t>
-  </si>
-  <si>
-    <t>Perché l'OSS 12 è rilevante per un'azienda di distribuzione e produzione di prodotti chimici?</t>
-  </si>
-  <si>
-    <t>Media · Scelta singola</t>
-  </si>
-  <si>
-    <t>Perché la sostenibilità riguarda solo le relazioni annuali.</t>
-  </si>
-  <si>
-    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
-  </si>
-  <si>
-    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
-  </si>
-  <si>
-    <t>Perché gli imballaggi, il riciclaggio e la responsabilità dei fornitori possono influire sulle prestazioni di sostenibilità.</t>
-  </si>
-  <si>
-    <t>Gli imballaggi, il riciclaggio e la responsabilità dei fornitori sono ambiti concreti in cui un'azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle scelte operative quotidiane.</t>
-  </si>
-  <si>
-    <t>Quale affermazione è un malinteso comune sull'OSS 12?</t>
-  </si>
-  <si>
-    <t>Il solo riciclaggio risolve tutti i problemi di consumo.</t>
-  </si>
-  <si>
-    <t>L'OSS 12 può essere collegato alle decisioni quotidiane.</t>
-  </si>
-  <si>
-    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
-  </si>
-  <si>
-    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
-  </si>
-  <si>
-    <t>Questo è il malinteso: restringe troppo la portata dell'OSS e nasconde opportunità pratiche. Una buona domanda a quiz spesso mette in discussione un'idea errata, perché rende l'apprendimento memorabile.</t>
-  </si>
-  <si>
-    <t>Quale comportamento traduce meglio l'OSS 12 dalla teoria all'azione?</t>
-  </si>
-  <si>
-    <t>Aspettare che qualcun altro risolva tutto.</t>
-  </si>
-  <si>
-    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
-  </si>
-  <si>
-    <t>Parlare di sostenibilità senza cambiare nulla.</t>
-  </si>
-  <si>
-    <t>Fare il contrario quando nessuno controlla.</t>
-  </si>
-  <si>
-    <t>Un'azione concreta genera apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico dei comportamenti.</t>
-  </si>
-  <si>
-    <t>Cosa rende l'OSS 12 un tema di apprendimento utile per i dipendenti?</t>
-  </si>
-  <si>
-    <t>Non ha alcun rapporto con la cultura aziendale.</t>
-  </si>
-  <si>
-    <t>Elimina la necessità di conoscenze specialistiche.</t>
-  </si>
-  <si>
-    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
-  </si>
-  <si>
-    <t>Fornisce una risposta perfetta per ogni situazione.</t>
-  </si>
-  <si>
-    <t>L'apprendimento più efficace avviene quando le persone vedono il legame tra obiettivi globali e scelte familiari. Gli OSS sono più coinvolgenti quando risultano pertinenti, concreti e connessi ai ruoli delle persone.</t>
-  </si>
-  <si>
-    <t>Quanti imballaggi riutilizzabili ha immesso in circolazione STOCKMEIER Chemie?</t>
-  </si>
-  <si>
-    <t>Zero tonnellate</t>
-  </si>
-  <si>
-    <t>Solo un pallet</t>
-  </si>
-  <si>
-    <t>6,2 chilogrammi</t>
-  </si>
-  <si>
-    <t>6.255,4 tonnellate</t>
-  </si>
-  <si>
-    <t>Il rapporto indica 6.255,4 tonnellate di imballaggi riutilizzabili. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>Quali materiali risultano riciclati al 100%?</t>
-  </si>
-  <si>
-    <t>Difficile · Scelta singola</t>
-  </si>
-  <si>
-    <t>Cartone, pallet e pellicole</t>
-  </si>
-  <si>
-    <t>Tutti i rifiuti liquidi pericolosi</t>
-  </si>
-  <si>
-    <t>Solo i bicchieri da caffè dell'ufficio</t>
-  </si>
-  <si>
-    <t>Tutte le materie prime nel mondo</t>
-  </si>
-  <si>
-    <t>Il rapporto indica che cartone, pallet e pellicole sono riciclati al 100%. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>Che cosa dimostra l'esempio delle clip per fusti?</t>
-  </si>
-  <si>
-    <t>I rifiuti dovrebbero essere sempre ignorati.</t>
-  </si>
-  <si>
-    <t>Il pensiero circolare può ridurre i rifiuti e i nuovi acquisti.</t>
-  </si>
-  <si>
-    <t>I materiali di piccole dimensioni non contano mai.</t>
-  </si>
-  <si>
-    <t>Il riutilizzo tra sedi diverse è impossibile.</t>
-  </si>
-  <si>
-    <t>Il rapporto descrive la restituzione di 650 clip per fusti destinate al riutilizzo, riducendo il consumo di materiali e i costi. Gli esempi di STOCKMEIER rendono concreto l'OSS e mostrano come le iniziative del Gruppo siano collegate agli obiettivi globali.</t>
-  </si>
-  <si>
-    <t>A casa, quale azione sostiene meglio l'OSS 12?</t>
-  </si>
-  <si>
-    <t>Acquistare più del necessario</t>
-  </si>
-  <si>
-    <t>Gettare prodotti ancora utilizzabili</t>
-  </si>
-  <si>
-    <t>Riparare o riutilizzare gli oggetti prima di sostituirli</t>
-  </si>
-  <si>
-    <t>Ignorare la raccolta differenziata</t>
-  </si>
-  <si>
-    <t>Il riutilizzo e la riparazione riducono la domanda di risorse. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
-  </si>
-  <si>
-    <t>Quale abitudine di acquisto favorisce il consumo responsabile?</t>
-  </si>
-  <si>
-    <t>Ignorare la durata del prodotto</t>
-  </si>
-  <si>
-    <t>Acquistare duplicati senza necessità</t>
-  </si>
-  <si>
-    <t>Scegliere ogni volta imballaggi eccessivi</t>
-  </si>
-  <si>
-    <t>Pianificare gli acquisti per evitare sprechi</t>
-  </si>
-  <si>
-    <t>La pianificazione riduce i consumi inutili e i rifiuti. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1459,224 +1475,236 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+  <dxfs count="76">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1691,10 +1719,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
   <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -1702,10 +1726,10 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="option1" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="option2" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="option3" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="option4" dataDxfId="72"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
@@ -1715,114 +1739,114 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3469E9C-5179-4439-94AE-5196570CDD78}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="60" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3469E9C-5179-4439-94AE-5196570CDD78}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="A1:J11" xr:uid="{A3469E9C-5179-4439-94AE-5196570CDD78}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9AF92849-245F-4A05-9642-BED555B4D475}" name="type" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{0F93932B-0B34-40A6-AEF4-45652D0CA6F7}" name="question" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{7F89349B-054F-47C4-B7AF-2320E05EDEC8}" name="note" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{D30D661D-E0F6-4B3D-AF35-C2E8FE392BCB}" name="option1" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{BEC7536D-A400-43E3-90F7-19334B0BDB6C}" name="option2" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{E98BAA9A-80A1-4D7A-B0E8-9AFD5492DAAE}" name="option3" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{DC201839-F1DE-405D-B94C-D7B210CFA09D}" name="option4" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{80031442-34DF-4EA8-8E88-2AE029045553}" name="correct" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{EE65DD9B-82F7-4593-8147-526B9AC03CAC}" name="explanation" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{7E2AE49E-A33C-47A7-9FEB-126FE74BEDD0}" name="Comments ZF" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{9AF92849-245F-4A05-9642-BED555B4D475}" name="type" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{0F93932B-0B34-40A6-AEF4-45652D0CA6F7}" name="question" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{7F89349B-054F-47C4-B7AF-2320E05EDEC8}" name="note" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{D30D661D-E0F6-4B3D-AF35-C2E8FE392BCB}" name="option1" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{BEC7536D-A400-43E3-90F7-19334B0BDB6C}" name="option2" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{E98BAA9A-80A1-4D7A-B0E8-9AFD5492DAAE}" name="option3" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{DC201839-F1DE-405D-B94C-D7B210CFA09D}" name="option4" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{80031442-34DF-4EA8-8E88-2AE029045553}" name="correct" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{EE65DD9B-82F7-4593-8147-526B9AC03CAC}" name="explanation" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{7E2AE49E-A33C-47A7-9FEB-126FE74BEDD0}" name="Comments ZF" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0988D1E6-705C-4ADD-B43A-EA29657E3232}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0" headerRowDxfId="48" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0988D1E6-705C-4ADD-B43A-EA29657E3232}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
   <autoFilter ref="A1:J11" xr:uid="{0988D1E6-705C-4ADD-B43A-EA29657E3232}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{579BA00B-14C5-480A-8505-48B70D1FC278}" name="type" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{312A9E3D-B0B4-4BEE-A9E6-62C459C73707}" name="question" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{59A6F5C6-60FD-4CFC-BDB2-8A2776DA440F}" name="note" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{DCA61397-EFBA-4D00-883B-165CF164A81B}" name="option1" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{3BCED57D-8ABE-4027-A617-0DFD873884B6}" name="option2" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{FF4C7038-CEFA-489D-A667-E23B8219B511}" name="option3" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{5E430F69-F11C-411B-B323-FB825D14169C}" name="option4" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{1854EF86-D036-489A-A832-20331496A27D}" name="correct" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{91A77087-B3A2-48D7-BB02-F0FDF046AAF3}" name="explanation" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{D22CD8F0-A0EA-4756-B906-E53FDA85E224}" name="Comments ZF" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{579BA00B-14C5-480A-8505-48B70D1FC278}" name="type" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{312A9E3D-B0B4-4BEE-A9E6-62C459C73707}" name="question" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{59A6F5C6-60FD-4CFC-BDB2-8A2776DA440F}" name="note" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{DCA61397-EFBA-4D00-883B-165CF164A81B}" name="option1" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{3BCED57D-8ABE-4027-A617-0DFD873884B6}" name="option2" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{FF4C7038-CEFA-489D-A667-E23B8219B511}" name="option3" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{5E430F69-F11C-411B-B323-FB825D14169C}" name="option4" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{1854EF86-D036-489A-A832-20331496A27D}" name="correct" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{91A77087-B3A2-48D7-BB02-F0FDF046AAF3}" name="explanation" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{D22CD8F0-A0EA-4756-B906-E53FDA85E224}" name="Comments ZF" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{978D7EA2-7E12-4B42-9C45-63EA9B659F03}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11" totalsRowShown="0" headerRowDxfId="36" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{978D7EA2-7E12-4B42-9C45-63EA9B659F03}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:J11" xr:uid="{978D7EA2-7E12-4B42-9C45-63EA9B659F03}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{CEE77700-54AB-4798-9B0E-4A023C4F7375}" name="type" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{3342B778-D980-43E1-B728-D5AFD9DA5A30}" name="question" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{47C5701D-18A2-4DEC-8145-7F365ADD62D5}" name="note" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{20553EC1-BB89-47B6-9F36-B8343EFC88C4}" name="option1" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{52E0A044-560E-4B7A-8D49-EBA8F6A9A74E}" name="option2" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{E6F4FAA8-7A4C-4E1E-8339-6B78EEBCBC65}" name="option3" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{C90E7B8C-8606-4B4D-A8E7-7E5A46BE4D0C}" name="option4" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{9A64C778-7242-4CAA-980E-5267D0DF5733}" name="correct" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{9D1B062C-EC9C-4464-A0E5-7463754A3293}" name="explanation" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{AFB526EA-97C2-4D53-BB92-C0B303ACD1DC}" name="Comments ZF" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{CEE77700-54AB-4798-9B0E-4A023C4F7375}" name="type" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{3342B778-D980-43E1-B728-D5AFD9DA5A30}" name="question" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{47C5701D-18A2-4DEC-8145-7F365ADD62D5}" name="note" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{20553EC1-BB89-47B6-9F36-B8343EFC88C4}" name="option1" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{52E0A044-560E-4B7A-8D49-EBA8F6A9A74E}" name="option2" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{E6F4FAA8-7A4C-4E1E-8339-6B78EEBCBC65}" name="option3" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{C90E7B8C-8606-4B4D-A8E7-7E5A46BE4D0C}" name="option4" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{9A64C778-7242-4CAA-980E-5267D0DF5733}" name="correct" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{9D1B062C-EC9C-4464-A0E5-7463754A3293}" name="explanation" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{AFB526EA-97C2-4D53-BB92-C0B303ACD1DC}" name="Comments ZF" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{182F318F-807C-47AD-A90B-6CB8E1AD463B}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0" headerRowDxfId="24" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{182F318F-807C-47AD-A90B-6CB8E1AD463B}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A1:J11" xr:uid="{182F318F-807C-47AD-A90B-6CB8E1AD463B}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B9D7087E-FD36-446B-AF82-299A563B621F}" name="type" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{413457F5-DE03-4C5A-842B-EAC5699009CE}" name="question" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{2DE94903-E3BE-4D0B-9D1B-AAE298B0FCB1}" name="note" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{A243F2A9-C60E-4479-B121-34F43B2BEFDB}" name="option1" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{89116CFA-4143-4C4C-A636-F5DDAF7774ED}" name="option2" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{DC6E2794-550C-41B1-BDCE-3B34AAB0161D}" name="option3" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{B1D6238C-0FDF-4996-8CD6-EA850B32030A}" name="option4" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{523389F7-EA92-41CF-B763-B0AAA7AC459A}" name="correct" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{01E2ED43-0F9F-406B-B2F9-53D06D6FA716}" name="explanation" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{415578DC-1EAE-42F7-A45D-38B5DB2986D3}" name="Comments ZF" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{B9D7087E-FD36-446B-AF82-299A563B621F}" name="type" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{413457F5-DE03-4C5A-842B-EAC5699009CE}" name="question" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{2DE94903-E3BE-4D0B-9D1B-AAE298B0FCB1}" name="note" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{A243F2A9-C60E-4479-B121-34F43B2BEFDB}" name="option1" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{89116CFA-4143-4C4C-A636-F5DDAF7774ED}" name="option2" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{DC6E2794-550C-41B1-BDCE-3B34AAB0161D}" name="option3" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{B1D6238C-0FDF-4996-8CD6-EA850B32030A}" name="option4" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{523389F7-EA92-41CF-B763-B0AAA7AC459A}" name="correct" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{01E2ED43-0F9F-406B-B2F9-53D06D6FA716}" name="explanation" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{415578DC-1EAE-42F7-A45D-38B5DB2986D3}" name="Comments ZF" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6BBDEC73-BA54-472E-A05F-B229399B10D4}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6BBDEC73-BA54-472E-A05F-B229399B10D4}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:J11" xr:uid="{6BBDEC73-BA54-472E-A05F-B229399B10D4}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1EAB0124-79BA-4AF4-819C-856D9A11A9A2}" name="type" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{9F5BC9B0-06DC-46F7-B583-7110D970EEEA}" name="question" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{39B4F923-E4C2-4301-B4BA-C6BD3C9B0BBE}" name="note" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{47829BDB-6BA6-4206-83FD-F23E7223C83D}" name="option1" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{265440E0-9BEA-47A9-A31F-358067CA4574}" name="option2" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{E9CBE778-4002-4E63-AF52-80EECE9796C0}" name="option3" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{06FF1C9E-3A5C-4231-9E1F-51D7D6DF72CD}" name="option4" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{738608F4-6AC4-418B-86B8-D3923CC87012}" name="correct" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D0263847-0B00-4AA8-A0FA-0C9892D0F35F}" name="explanation" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{8A7622E5-3786-40CC-A93D-053EB22D8B88}" name="Comments ZF" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{1EAB0124-79BA-4AF4-819C-856D9A11A9A2}" name="type" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9F5BC9B0-06DC-46F7-B583-7110D970EEEA}" name="question" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{39B4F923-E4C2-4301-B4BA-C6BD3C9B0BBE}" name="note" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{47829BDB-6BA6-4206-83FD-F23E7223C83D}" name="option1" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{265440E0-9BEA-47A9-A31F-358067CA4574}" name="option2" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{E9CBE778-4002-4E63-AF52-80EECE9796C0}" name="option3" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{06FF1C9E-3A5C-4231-9E1F-51D7D6DF72CD}" name="option4" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{738608F4-6AC4-418B-86B8-D3923CC87012}" name="correct" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{D0263847-0B00-4AA8-A0FA-0C9892D0F35F}" name="explanation" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{8A7622E5-3786-40CC-A93D-053EB22D8B88}" name="Comments ZF" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8080ED94-5AC4-4CA3-9911-8E5F8574BD31}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8080ED94-5AC4-4CA3-9911-8E5F8574BD31}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:J11" xr:uid="{8080ED94-5AC4-4CA3-9911-8E5F8574BD31}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A7B5ABBE-9948-4D73-A983-2AB27DFD0605}" name="type" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{96360C7C-7896-4FF1-81C0-80C116A3BEF7}" name="question" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{87A80A98-CA9B-40F6-8B74-A5E46BC10F8D}" name="note" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{3F1DCEB0-A625-4DD2-A78A-0569F5881A2C}" name="option1" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{C74B4EEA-AEBD-4A20-9EC8-A02AAB954213}" name="option2" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{500CFAF5-B4EB-4269-8749-30E624FA3F3D}" name="option3" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{48561FCA-AFC8-4913-BB7A-C97FA39576E3}" name="option4" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{B544586B-F8D6-450D-ADF0-22B4AC9C048A}" name="correct" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{7B5413F8-2CE9-497D-A170-02883C1017D1}" name="explanation" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{D6CF86FB-EF00-4D01-8260-3D809E42F3DD}" name="Comments ZF" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{A7B5ABBE-9948-4D73-A983-2AB27DFD0605}" name="type" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{96360C7C-7896-4FF1-81C0-80C116A3BEF7}" name="question" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{87A80A98-CA9B-40F6-8B74-A5E46BC10F8D}" name="note" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{3F1DCEB0-A625-4DD2-A78A-0569F5881A2C}" name="option1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{C74B4EEA-AEBD-4A20-9EC8-A02AAB954213}" name="option2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{500CFAF5-B4EB-4269-8749-30E624FA3F3D}" name="option3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{48561FCA-AFC8-4913-BB7A-C97FA39576E3}" name="option4" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B544586B-F8D6-450D-ADF0-22B4AC9C048A}" name="correct" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{7B5413F8-2CE9-497D-A170-02883C1017D1}" name="explanation" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{D6CF86FB-EF00-4D01-8260-3D809E42F3DD}" name="Comments ZF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2114,7 +2138,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2125,7 +2149,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2157,7 +2181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45.75">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2187,7 +2211,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="45.75">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2217,7 +2241,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45.75">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2247,7 +2271,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45.75">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2277,7 +2301,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="45.75">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2307,7 +2331,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="30.75">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2337,7 +2361,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45.75">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2367,7 +2391,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45.75">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2397,7 +2421,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45.75">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2427,7 +2451,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="30.75">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2468,12 +2492,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D79F67-3C71-475B-B84E-E46FB79D4B0A}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="72" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2505,7 +2529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="213">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2535,7 +2559,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="198">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2565,7 +2589,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="167.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2595,7 +2619,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="152.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2625,7 +2649,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="198">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2655,7 +2679,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="198">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2685,7 +2709,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="198">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2715,7 +2739,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="259.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2745,7 +2769,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="198">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2775,7 +2799,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="183">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2816,12 +2840,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045AA95C-956B-431E-82CC-5F1E358F38C7}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="72" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2853,7 +2877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="229.5">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2883,7 +2907,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="213">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2913,7 +2937,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="213">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2943,7 +2967,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="167.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2973,7 +2997,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="198">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3003,7 +3027,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="198">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3033,7 +3057,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="198">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3063,7 +3087,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="244.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3093,7 +3117,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="229.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3123,7 +3147,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="229.5">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3164,12 +3188,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323579A6-FF01-451B-A839-B64663BB716B}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="45.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3201,7 +3234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="106.5">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3231,7 +3264,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="106.5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3261,7 +3294,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="76.5">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3291,7 +3324,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="91.5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3321,7 +3354,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="91.5">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3351,7 +3384,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="60.75">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3381,7 +3414,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45.75">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3411,7 +3444,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="76.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3441,7 +3474,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="91.5">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3471,7 +3504,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="76.5">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3512,12 +3545,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6473EC08-02A2-4770-BD9B-BF02ADA58374}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="72" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3549,7 +3582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="198">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3579,7 +3612,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="198">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3609,7 +3642,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="198">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3639,7 +3672,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="137.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3669,7 +3702,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="229.5">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3699,7 +3732,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="198">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3729,7 +3762,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="198">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3759,7 +3792,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="259.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3789,7 +3822,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="183">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3819,7 +3852,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="183">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3860,18 +3893,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D766D4-C9A4-46FC-88B2-414523597B13}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="43.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3903,303 +3936,303 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60.75">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>329</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2">
         <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>395</v>
+        <v>332</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60.75">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>396</v>
+        <v>333</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>400</v>
+        <v>337</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2">
         <v>4</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>402</v>
+        <v>339</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="60.75">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>405</v>
+        <v>342</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>406</v>
+        <v>343</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>407</v>
+        <v>344</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>408</v>
+        <v>345</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45.75">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>409</v>
+        <v>346</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>410</v>
+        <v>347</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="60.75">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>415</v>
+        <v>352</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>416</v>
+        <v>353</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>417</v>
+        <v>354</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>419</v>
+        <v>356</v>
       </c>
       <c r="H6" s="2">
         <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="60.75">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>422</v>
+        <v>359</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>423</v>
+        <v>360</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>424</v>
+        <v>361</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="H7" s="2">
         <v>4</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>426</v>
+        <v>363</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="60.75">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>427</v>
+        <v>364</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>428</v>
+        <v>365</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>429</v>
+        <v>366</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>430</v>
+        <v>367</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>431</v>
+        <v>368</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>432</v>
+        <v>369</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>433</v>
+        <v>370</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="76.5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>434</v>
+        <v>371</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>428</v>
+        <v>365</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>436</v>
+        <v>373</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>437</v>
+        <v>374</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>438</v>
+        <v>375</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>439</v>
+        <v>376</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="60.75">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>441</v>
+        <v>378</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>442</v>
+        <v>379</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>443</v>
+        <v>380</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>444</v>
+        <v>381</v>
       </c>
       <c r="H10" s="2">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>445</v>
+        <v>382</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45.75">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>446</v>
+        <v>383</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>450</v>
+        <v>387</v>
       </c>
       <c r="H11" s="2">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>451</v>
+        <v>388</v>
       </c>
       <c r="J11" s="2"/>
     </row>
@@ -4214,12 +4247,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCED6B28-9F1A-4C9B-9484-DCCDBC33DBA7}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="10" width="18.1796875" customWidth="1"/>
+    <col min="1" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="72" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4251,303 +4284,303 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="198">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>328</v>
+        <v>391</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="H2" s="2">
         <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="213">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>396</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>335</v>
+        <v>398</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="H3" s="2">
         <v>4</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="198">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>344</v>
+        <v>407</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="137.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="213">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>356</v>
+        <v>419</v>
       </c>
       <c r="H6" s="2">
         <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>357</v>
+        <v>420</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="167.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>360</v>
+        <v>423</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>361</v>
+        <v>424</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="H7" s="2">
         <v>4</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>363</v>
+        <v>426</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="183">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>370</v>
+        <v>433</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="198">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>371</v>
+        <v>434</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>375</v>
+        <v>438</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="183">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>378</v>
+        <v>441</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>381</v>
+        <v>444</v>
       </c>
       <c r="H10" s="2">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="183">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>383</v>
+        <v>446</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>387</v>
+        <v>450</v>
       </c>
       <c r="H11" s="2">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="J11" s="2"/>
     </row>
@@ -4560,25 +4593,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -4742,38 +4756,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7BFB3FE-1173-4263-B2E8-20EA39608C03}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF5E1DC1-3055-4B42-B3F2-6C6234814DF7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B9E12B-AF75-461E-A4A5-D812641AB2B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B9E12B-AF75-461E-A4A5-D812641AB2B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB98C1-CBF8-47DD-ACAD-99571B2C850D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7BFB3FE-1173-4263-B2E8-20EA39608C03}"/>
 </file>